--- a/slide_classification/SurGen_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/SurGen_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,19 +468,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9294871794871795</v>
+        <v>0.8589743589743589</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8846153846153846</v>
+        <v>0.8926174496644296</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.8711656441717791</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9051385442514475</v>
+        <v>0.8699750774883562</v>
       </c>
     </row>
     <row r="3">
@@ -489,19 +490,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.752482269503546</v>
+        <v>0.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6978723404255319</v>
+        <v>0.5566137566137566</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5595238095238095</v>
+        <v>0.5096846846846848</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6488095238095238</v>
+        <v>0.6829736211031174</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6646719858156027</v>
+        <v>0.6123180156003897</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +512,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7769980506822611</v>
+        <v>0.6703803303880138</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6866071428571429</v>
+        <v>0.5712230215827339</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5794899620184482</v>
+        <v>0.5088247955230306</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6736842105263158</v>
+        <v>0.6540032679738562</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6791948415210419</v>
+        <v>0.6011078538669087</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9259409206777628</v>
+        <v>0.8685638858516307</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8878090659340659</v>
+        <v>0.8726860122640143</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8770412896224598</v>
+        <v>0.8530486017393418</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8943972835314091</v>
+        <v>0.8674719887955182</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8962971399414245</v>
+        <v>0.8654426221626264</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.8558035714285714</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8591016548463357</v>
+        <v>0.7153439153439154</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8157142857142857</v>
+        <v>0.6882882882882884</v>
       </c>
       <c r="E6" t="n">
-        <v>0.84</v>
+        <v>0.8911270983213428</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8620373184734886</v>
+        <v>0.7876407183455296</v>
       </c>
     </row>
     <row r="7">
@@ -578,31 +579,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[137   4]
- [  7   8]]</t>
+          <t>[[126, 14], [8, 8]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[131  10]
- [  8   7]]</t>
+          <t>[[131, 4], [12, 2]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[138   2]
- [ 13   2]]</t>
+          <t>[[141, 7], [14, 1]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[135   5]
- [ 10   5]]</t>
+          <t>[[125, 14], [8, 7]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[[135, 5], [10, 6]]</t>
+          <t>[[131, 10], [10, 4]]</t>
         </is>
       </c>
     </row>
@@ -613,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8141025641025641</v>
+        <v>0.8012820512820513</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7449664429530202</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8516129032258064</v>
+        <v>0.7239263803680982</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8</v>
+        <v>0.7987012987012987</v>
       </c>
       <c r="F8" t="n">
-        <v>0.824762200165426</v>
+        <v>0.767219043326117</v>
       </c>
     </row>
     <row r="9">
@@ -635,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.74822695035461</v>
+        <v>0.5848214285714286</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7588652482269503</v>
+        <v>0.6031746031746031</v>
       </c>
       <c r="D9" t="n">
-        <v>0.769047619047619</v>
+        <v>0.5484234234234234</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6511904761904762</v>
+        <v>0.5911270983213429</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7318325734549138</v>
+        <v>0.5818866383726995</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6489485528051524</v>
+        <v>0.5647556475564756</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6685191238966982</v>
+        <v>0.5433870967741936</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6894869784861946</v>
+        <v>0.5078832606507884</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5970649895178197</v>
+        <v>0.5638987850552664</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6510049111764663</v>
+        <v>0.5449811975091809</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8434289773235997</v>
+        <v>0.8197928133127486</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8573063092513894</v>
+        <v>0.7897618532149816</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8704310909187972</v>
+        <v>0.7739363617841422</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8276729559748428</v>
+        <v>0.821558180560647</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8497098333671573</v>
+        <v>0.8012623022181298</v>
       </c>
     </row>
     <row r="12">
@@ -701,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7683215130023641</v>
+        <v>0.5901785714285714</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8146572104018913</v>
+        <v>0.6375661375661377</v>
       </c>
       <c r="D12" t="n">
-        <v>0.879047619047619</v>
+        <v>0.5617117117117117</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6795238095238095</v>
+        <v>0.7184652278177458</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7853875379939209</v>
+        <v>0.6269804121310416</v>
       </c>
     </row>
     <row r="13">
@@ -724,31 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[117  24]
- [  5  10]]</t>
+          <t>[[120, 20], [11, 5]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[120  21]
- [  5  10]]</t>
+          <t>[[105, 30], [8, 6]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[122  18]
- [  5  10]]</t>
+          <t>[[113, 35], [10, 5]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[117  23]
- [  8   7]]</t>
+          <t>[[118, 21], [10, 5]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[119, 22], [6, 9]]</t>
+          <t>[[114, 26], [10, 5]]</t>
         </is>
       </c>
     </row>
@@ -759,19 +752,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9294871794871795</v>
+        <v>0.8859060402684564</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.901840490797546</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8967741935483871</v>
+        <v>0.8961038961038961</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9067307692307693</v>
+        <v>0.8921164529463208</v>
       </c>
     </row>
     <row r="15">
@@ -781,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.526241134751773</v>
+        <v>0.4928571428571429</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5892857142857143</v>
+        <v>0.5265765765765766</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5261904761904762</v>
+        <v>0.4964028776978417</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5687626646403242</v>
+        <v>0.5011813715051125</v>
       </c>
     </row>
     <row r="16">
@@ -803,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5283446712018141</v>
+        <v>0.4693877551020408</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6917549847314532</v>
+        <v>0.4697508896797153</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6169055857637172</v>
+        <v>0.5295815295815296</v>
       </c>
       <c r="E16" t="n">
-        <v>0.528158295281583</v>
+        <v>0.4726027397260274</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5912908842446419</v>
+        <v>0.4853307285223283</v>
       </c>
     </row>
     <row r="17">
@@ -825,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8653410081981511</v>
+        <v>0.8424908424908426</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9103991930469386</v>
+        <v>0.8512264443860612</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8839953438680975</v>
+        <v>0.8710328526279445</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8644866696126086</v>
+        <v>0.8531400106742572</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8810555536814491</v>
+        <v>0.8544725375447765</v>
       </c>
     </row>
     <row r="18">
@@ -847,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6078014184397164</v>
+        <v>0.58125</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6278959810874705</v>
+        <v>0.5396825396825397</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6504761904761905</v>
+        <v>0.5166666666666667</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.5460431654676259</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6233291117865587</v>
+        <v>0.5459105929542081</v>
       </c>
     </row>
     <row r="19">
@@ -870,31 +863,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[139   2]
- [ 14   1]]</t>
+          <t>[[138, 2], [16, 0]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[141   0]
- [ 11   4]]</t>
+          <t>[[132, 3], [14, 0]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[137   3]
- [ 12   3]]</t>
+          <t>[[146, 2], [14, 1]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[138   2]
- [ 14   1]]</t>
+          <t>[[138, 1], [15, 0]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[139, 2], [13, 2]]</t>
+          <t>[[138, 2], [15, 0]]</t>
         </is>
       </c>
     </row>
@@ -905,19 +894,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6474358974358975</v>
+        <v>0.6644295302013423</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7225806451612903</v>
+        <v>0.5828220858895705</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6258064516129033</v>
+        <v>0.6558441558441559</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6624172870140612</v>
+        <v>0.6584662506760748</v>
       </c>
     </row>
     <row r="21">
@@ -927,19 +916,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5964539007092198</v>
+        <v>0.5907407407407408</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6976190476190476</v>
+        <v>0.5605855855855856</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5845238095238094</v>
+        <v>0.6309352517985611</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6196491894630192</v>
+        <v>0.602708251674079</v>
       </c>
     </row>
     <row r="22">
@@ -949,19 +938,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.50271546635183</v>
+        <v>0.5552538691284279</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4985681725206008</v>
+        <v>0.5025373931623931</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5716856243172033</v>
+        <v>0.4547422274695002</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4852267521759047</v>
+        <v>0.5149462173887205</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5145490038413847</v>
+        <v>0.5068699267872604</v>
       </c>
     </row>
     <row r="23">
@@ -971,19 +960,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7241394968667696</v>
+        <v>0.7773345307963825</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7192426823950405</v>
+        <v>0.7329956117707795</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7767060330727563</v>
+        <v>0.6703703435437959</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7021707327885567</v>
+        <v>0.7254443423100937</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7305647362807808</v>
+        <v>0.7265362071052629</v>
       </c>
     </row>
     <row r="24">
@@ -993,19 +982,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5900709219858157</v>
+        <v>0.6977678571428572</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5910165484633569</v>
+        <v>0.6507936507936509</v>
       </c>
       <c r="D24" t="n">
-        <v>0.758095238095238</v>
+        <v>0.577027027027027</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.6028776978417266</v>
       </c>
       <c r="F24" t="n">
-        <v>0.638129010469436</v>
+        <v>0.6321165582013154</v>
       </c>
     </row>
     <row r="25">
@@ -1016,31 +1005,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[94 47]
- [ 7  8]]</t>
+          <t>[[106, 34], [8, 8]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[93 48]
- [ 7  8]]</t>
+          <t>[[92, 43], [7, 7]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[102  38]
- [  5  10]]</t>
+          <t>[[87, 61], [7, 8]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[89 51]
- [ 7  8]]</t>
+          <t>[[92, 47], [6, 9]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>[[94, 46], [6, 8]]</t>
+          <t>[[94, 46], [7, 8]]</t>
         </is>
       </c>
     </row>
@@ -1051,19 +1036,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8589743589743589</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9102564102564102</v>
+        <v>0.8791946308724832</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9096774193548387</v>
+        <v>0.901840490797546</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8838709677419355</v>
+        <v>0.8766233766233766</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9003101736972705</v>
+        <v>0.8791582143169412</v>
       </c>
     </row>
     <row r="27">
@@ -1073,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.526241134751773</v>
+        <v>0.4785714285714286</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5929078014184397</v>
+        <v>0.4851851851851852</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5630952380952381</v>
+        <v>0.4966216216216216</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4892857142857143</v>
+        <v>0.515347721822542</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5428824721377913</v>
+        <v>0.4939314893001944</v>
       </c>
     </row>
     <row r="28">
@@ -1095,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5283446712018141</v>
+        <v>0.4620689655172414</v>
       </c>
       <c r="C28" t="n">
-        <v>0.626027397260274</v>
+        <v>0.4678571428571429</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5871385083713851</v>
+        <v>0.4741935483870968</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4691780821917808</v>
+        <v>0.5145180023228804</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5526721647563135</v>
+        <v>0.4796594147710903</v>
       </c>
     </row>
     <row r="29">
@@ -1117,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8653410081981511</v>
+        <v>0.8293545534924845</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8893572181243414</v>
+        <v>0.8477948226270374</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8814258359110325</v>
+        <v>0.8611122105679794</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8475475033141846</v>
+        <v>0.8521200054301099</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8709178913869274</v>
+        <v>0.8475953980294029</v>
       </c>
     </row>
     <row r="30">
@@ -1139,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7654846335697399</v>
+        <v>0.7276785714285714</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8056737588652482</v>
+        <v>0.6306878306878307</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8038095238095238</v>
+        <v>0.7063063063063063</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6638095238095238</v>
+        <v>0.705515587529976</v>
       </c>
       <c r="F30" t="n">
-        <v>0.759694360013509</v>
+        <v>0.6925470739881711</v>
       </c>
     </row>
     <row r="31">
@@ -1162,31 +1147,413 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[139   2]
- [ 14   1]]</t>
+          <t>[[134, 6], [16, 0]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[139   2]
- [ 12   3]]</t>
+          <t>[[131, 4], [14, 0]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[139   1]
- [ 13   2]]</t>
+          <t>[[147, 1], [15, 0]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[137   3]
- [ 15   0]]</t>
+          <t>[[134, 5], [14, 1]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[138, 2], [14, 2]]</t>
+          <t>[[136, 4], [15, 0]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>N_folds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>N_test</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>acc_sd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bacc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bacc_sd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_sd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1_sd</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>auroc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_sd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>conf_matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8699750774883562</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01414015694402949</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6123180156003897</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0811124374885151</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6011078538669087</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.06520327233901951</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8654426221626264</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.007415171244830949</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.7876407183455296</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.08725442462054858</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[[131, 10], [10, 4]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>622</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.767219043326117</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03361864736970973</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5818866383726995</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.02041423090469967</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5449811975091809</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02306351051736989</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8012623022181298</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.02021305189103009</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6269804121310416</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0593630942120938</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[[114, 26], [10, 5]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>622</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8921164529463208</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.007164004934422286</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5011813715051125</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.01490090899191792</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4853307285223283</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0255785304162571</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8544725375447765</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.01036964079265743</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5459105929542081</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02314566448649389</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[[138, 2], [15, 0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>proto</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>622</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6584662506760748</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05242183867579228</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.602708251674079</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.02908267427349742</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5068699267872604</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03585491678321843</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7265362071052629</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.03800654547836767</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6321165582013154</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04622957451822583</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[[94, 46], [7, 8]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Averaging</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Virchow2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>622</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8791582143169412</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01523401138186459</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4939314893001944</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.01394920363875341</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4796594147710903</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02057738047417887</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8475953980294029</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.01157523728616088</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6925470739881711</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03680450689645207</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[[136, 4], [15, 0]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/SurGen_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/SurGen_Results/Averaging/Virchow2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,13 +616,13 @@
         <v>0.7449664429530202</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7239263803680982</v>
+        <v>0.754601226993865</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7987012987012987</v>
+        <v>0.7792207792207793</v>
       </c>
       <c r="F8" t="n">
-        <v>0.767219043326117</v>
+        <v>0.7700176251124289</v>
       </c>
     </row>
     <row r="9">
@@ -635,16 +635,16 @@
         <v>0.5848214285714286</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6031746031746031</v>
+        <v>0.6351851851851852</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5484234234234234</v>
+        <v>0.5653153153153153</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5911270983213429</v>
+        <v>0.5803357314148681</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5818866383726995</v>
+        <v>0.5914144151216992</v>
       </c>
     </row>
     <row r="10">
@@ -657,16 +657,16 @@
         <v>0.5647556475564756</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5433870967741936</v>
+        <v>0.5573796122576611</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5078832606507884</v>
+        <v>0.527536231884058</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5638987850552664</v>
+        <v>0.5492424242424242</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5449811975091809</v>
+        <v>0.5497284789851546</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         <v>0.8197928133127486</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7897618532149816</v>
+        <v>0.7913796794137277</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7739363617841422</v>
+        <v>0.7947897217035654</v>
       </c>
       <c r="E11" t="n">
-        <v>0.821558180560647</v>
+        <v>0.8084907516725698</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8012623022181298</v>
+        <v>0.8036132415256529</v>
       </c>
     </row>
     <row r="12">
@@ -701,16 +701,16 @@
         <v>0.5901785714285714</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6375661375661377</v>
+        <v>0.6878306878306878</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5617117117117117</v>
+        <v>0.5400900900900901</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7184652278177458</v>
+        <v>0.724220623501199</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6269804121310416</v>
+        <v>0.6355799932126371</v>
       </c>
     </row>
     <row r="13">
@@ -726,22 +726,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[105, 30], [8, 6]]</t>
+          <t>[[104, 31], [7, 7]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[113, 35], [10, 5]]</t>
+          <t>[[118, 30], [10, 5]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[118, 21], [10, 5]]</t>
+          <t>[[115, 24], [10, 5]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[114, 26], [10, 5]]</t>
+          <t>[[114, 26], [10, 6]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>622</v>
       </c>
       <c r="F3" t="n">
-        <v>0.767219043326117</v>
+        <v>0.7700176251124289</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03361864736970973</v>
+        <v>0.02195102188846658</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5818866383726995</v>
+        <v>0.5914144151216992</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02041423090469967</v>
+        <v>0.02628330281272791</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5449811975091809</v>
+        <v>0.5497284789851546</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02306351051736989</v>
+        <v>0.01393814654315285</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8012623022181298</v>
+        <v>0.8036132415256529</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02021305189103009</v>
+        <v>0.0113256698747156</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6269804121310416</v>
+        <v>0.6355799932126371</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0593630942120938</v>
+        <v>0.07376806071124269</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[114, 26], [10, 5]]</t>
+          <t>[[114, 26], [10, 6]]</t>
         </is>
       </c>
     </row>
